--- a/Team-Data/2013-14/12-22-2013-14.xlsx
+++ b/Team-Data/2013-14/12-22-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE2" t="n">
         <v>9</v>
@@ -751,7 +818,7 @@
         <v>9</v>
       </c>
       <c r="AH2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>10</v>
@@ -760,7 +827,7 @@
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL2" t="n">
         <v>7</v>
@@ -802,7 +869,7 @@
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
         <v>3</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -843,52 +910,52 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
         <v>12</v>
       </c>
       <c r="F3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.414</v>
+        <v>0.429</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>80.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.452</v>
+        <v>0.455</v>
       </c>
       <c r="L3" t="n">
         <v>6.5</v>
       </c>
       <c r="M3" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="N3" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="O3" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="P3" t="n">
-        <v>20.2</v>
+        <v>20.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.763</v>
+        <v>0.764</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S3" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T3" t="n">
         <v>41.4</v>
@@ -900,43 +967,43 @@
         <v>16</v>
       </c>
       <c r="W3" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
         <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA3" t="n">
         <v>18.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="AD3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AG3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH3" t="n">
         <v>26</v>
       </c>
       <c r="AI3" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AJ3" t="n">
         <v>26</v>
@@ -945,34 +1012,34 @@
         <v>12</v>
       </c>
       <c r="AL3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO3" t="n">
         <v>28</v>
       </c>
       <c r="AP3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AS3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT3" t="n">
         <v>23</v>
       </c>
       <c r="AU3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AV3" t="n">
         <v>24</v>
@@ -981,7 +1048,7 @@
         <v>27</v>
       </c>
       <c r="AX3" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
@@ -996,7 +1063,7 @@
         <v>24</v>
       </c>
       <c r="BC3" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -1103,13 +1170,13 @@
         <v>-4.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE4" t="n">
         <v>24</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
@@ -1154,7 +1221,7 @@
         <v>28</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV4" t="n">
         <v>9</v>
@@ -1169,7 +1236,7 @@
         <v>5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA4" t="n">
         <v>8</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -1285,28 +1352,28 @@
         <v>-1.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
       </c>
       <c r="AF5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
         <v>29</v>
       </c>
       <c r="AJ5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL5" t="n">
         <v>30</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -1467,10 +1534,10 @@
         <v>-1.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF6" t="n">
         <v>20</v>
@@ -1485,7 +1552,7 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>29</v>
@@ -1518,7 +1585,7 @@
         <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>27</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-5.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF7" t="n">
         <v>20</v>
@@ -1706,13 +1773,13 @@
         <v>15</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ7" t="n">
         <v>5</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1867,16 +1934,16 @@
         <v>17</v>
       </c>
       <c r="AP8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ8" t="n">
         <v>3</v>
       </c>
       <c r="AR8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS8" t="n">
         <v>22</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>21</v>
       </c>
       <c r="AT8" t="n">
         <v>26</v>
@@ -1891,7 +1958,7 @@
         <v>2</v>
       </c>
       <c r="AX8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>0.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
@@ -2028,7 +2095,7 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ9" t="n">
         <v>7</v>
@@ -2049,7 +2116,7 @@
         <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ9" t="n">
         <v>25</v>
@@ -2067,7 +2134,7 @@
         <v>15</v>
       </c>
       <c r="AV9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW9" t="n">
         <v>20</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2310,7 @@
         <v>26</v>
       </c>
       <c r="AT10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>23</v>
@@ -2258,19 +2325,19 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ10" t="n">
         <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB10" t="n">
         <v>15</v>
       </c>
       <c r="BC10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>9</v>
@@ -2395,7 +2462,7 @@
         <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK11" t="n">
         <v>9</v>
@@ -2425,7 +2492,7 @@
         <v>2</v>
       </c>
       <c r="AT11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>12</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2574,7 +2641,7 @@
         <v>11</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2589,7 +2656,7 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
         <v>1</v>
@@ -2619,7 +2686,7 @@
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
         <v>21</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2663,70 +2730,70 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" t="n">
         <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J13" t="n">
-        <v>79.5</v>
+        <v>79.3</v>
       </c>
       <c r="K13" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L13" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M13" t="n">
         <v>19.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="O13" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="P13" t="n">
         <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.783</v>
+        <v>0.787</v>
       </c>
       <c r="R13" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="T13" t="n">
-        <v>44.3</v>
+        <v>43.9</v>
       </c>
       <c r="U13" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W13" t="n">
         <v>7.4</v>
       </c>
       <c r="X13" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="Z13" t="n">
         <v>19.7</v>
@@ -2735,34 +2802,34 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.5</v>
+        <v>98.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1</v>
-      </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AI13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL13" t="n">
         <v>19</v>
@@ -2774,13 +2841,13 @@
         <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>25</v>
@@ -2789,22 +2856,22 @@
         <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ13" t="n">
         <v>9</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -2845,37 +2912,37 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" t="n">
         <v>9</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.679</v>
       </c>
       <c r="H14" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="J14" t="n">
-        <v>81.5</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L14" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="O14" t="n">
         <v>21.2</v>
@@ -2884,49 +2951,49 @@
         <v>29.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.718</v>
+        <v>0.716</v>
       </c>
       <c r="R14" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T14" t="n">
-        <v>43</v>
+        <v>42.9</v>
       </c>
       <c r="U14" t="n">
         <v>23.7</v>
       </c>
       <c r="V14" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="Y14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Z14" t="n">
         <v>22.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB14" t="n">
-        <v>105.1</v>
+        <v>104.5</v>
       </c>
       <c r="AC14" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -2935,16 +3002,16 @@
         <v>6</v>
       </c>
       <c r="AH14" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,10 +3020,10 @@
         <v>6</v>
       </c>
       <c r="AN14" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -2968,7 +3035,7 @@
         <v>21</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>15</v>
@@ -2977,13 +3044,13 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AY14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>13</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>-3.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE16" t="n">
         <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
         <v>20</v>
@@ -3302,7 +3369,7 @@
         <v>13</v>
       </c>
       <c r="AI16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ16" t="n">
         <v>22</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
         <v>26</v>
@@ -3341,7 +3408,7 @@
         <v>16</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE17" t="n">
         <v>5</v>
@@ -3508,7 +3575,7 @@
         <v>11</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-7.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>16</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB18" t="n">
         <v>28</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -3755,106 +3822,106 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
         <v>13</v>
       </c>
       <c r="F19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>0.464</v>
+        <v>0.481</v>
       </c>
       <c r="H19" t="n">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="J19" t="n">
-        <v>89.8</v>
+        <v>89.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.425</v>
+        <v>0.423</v>
       </c>
       <c r="L19" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
         <v>23.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.334</v>
+        <v>0.336</v>
       </c>
       <c r="O19" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="P19" t="n">
         <v>26.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.797</v>
+        <v>0.799</v>
       </c>
       <c r="R19" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="S19" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T19" t="n">
-        <v>46.1</v>
+        <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V19" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="W19" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X19" t="n">
         <v>2.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z19" t="n">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="AA19" t="n">
         <v>22.7</v>
       </c>
       <c r="AB19" t="n">
-        <v>105.6</v>
+        <v>105.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>13</v>
       </c>
       <c r="AF19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL19" t="n">
         <v>13</v>
@@ -3866,7 +3933,7 @@
         <v>26</v>
       </c>
       <c r="AO19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP19" t="n">
         <v>3</v>
@@ -3881,13 +3948,13 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AU19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AV19" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AW19" t="n">
         <v>3</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AZ19" t="n">
         <v>1</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4097,7 @@
         <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ20" t="n">
         <v>4</v>
@@ -4084,7 +4151,7 @@
         <v>22</v>
       </c>
       <c r="BA20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-3.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4263,7 +4330,7 @@
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BA21" t="n">
         <v>24</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4301,61 +4368,61 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" t="n">
         <v>22</v>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.846</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38.9</v>
+        <v>39.3</v>
       </c>
       <c r="J22" t="n">
-        <v>83.2</v>
+        <v>83.5</v>
       </c>
       <c r="K22" t="n">
-        <v>0.467</v>
+        <v>0.47</v>
       </c>
       <c r="L22" t="n">
         <v>6.5</v>
       </c>
       <c r="M22" t="n">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0.342</v>
+        <v>0.343</v>
       </c>
       <c r="O22" t="n">
-        <v>21.4</v>
+        <v>20.9</v>
       </c>
       <c r="P22" t="n">
-        <v>26</v>
+        <v>25.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.826</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="S22" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="T22" t="n">
         <v>47.4</v>
       </c>
       <c r="U22" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="W22" t="n">
         <v>8.300000000000001</v>
@@ -4364,22 +4431,22 @@
         <v>6.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>105.7</v>
+        <v>106</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4388,37 +4455,37 @@
         <v>1</v>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM22" t="n">
         <v>24</v>
       </c>
       <c r="AN22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>2</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1</v>
       </c>
       <c r="AR22" t="n">
         <v>12</v>
@@ -4430,25 +4497,25 @@
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV22" t="n">
         <v>26</v>
       </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX22" t="n">
         <v>1</v>
       </c>
       <c r="AY22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE23" t="n">
         <v>25</v>
@@ -4576,7 +4643,7 @@
         <v>10</v>
       </c>
       <c r="AI23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>17</v>
@@ -4621,10 +4688,10 @@
         <v>17</v>
       </c>
       <c r="AX23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>25</v>
@@ -4794,7 +4861,7 @@
         <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4937,16 +5004,16 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AJ25" t="n">
         <v>20</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>2</v>
@@ -4970,7 +5037,7 @@
         <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT25" t="n">
         <v>21</v>
@@ -4994,7 +5061,7 @@
         <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BB25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -5107,16 +5174,16 @@
         <v>6.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="n">
         <v>16</v>
@@ -5128,7 +5195,7 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5146,16 +5213,16 @@
         <v>16</v>
       </c>
       <c r="AQ26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AR26" t="n">
         <v>4</v>
       </c>
       <c r="AS26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU26" t="n">
         <v>5</v>
@@ -5167,7 +5234,7 @@
         <v>30</v>
       </c>
       <c r="AX26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY26" t="n">
         <v>3</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AE27" t="n">
         <v>25</v>
@@ -5307,7 +5374,7 @@
         <v>18</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
@@ -5319,10 +5386,10 @@
         <v>18</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP27" t="n">
         <v>9</v>
@@ -5340,13 +5407,13 @@
         <v>22</v>
       </c>
       <c r="AU27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>29</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -5471,10 +5538,10 @@
         <v>7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF28" t="n">
         <v>4</v>
@@ -5489,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
@@ -5534,7 +5601,7 @@
         <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>2</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F29" t="n">
         <v>14</v>
       </c>
       <c r="G29" t="n">
-        <v>0.44</v>
+        <v>0.417</v>
       </c>
       <c r="H29" t="n">
         <v>49</v>
@@ -5593,40 +5660,40 @@
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>83.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.433</v>
+        <v>0.434</v>
       </c>
       <c r="L29" t="n">
         <v>7.4</v>
       </c>
       <c r="M29" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.342</v>
+        <v>0.34</v>
       </c>
       <c r="O29" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.783</v>
+        <v>0.781</v>
       </c>
       <c r="R29" t="n">
         <v>12.2</v>
       </c>
       <c r="S29" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="V29" t="n">
         <v>14.9</v>
@@ -5635,43 +5702,43 @@
         <v>7.2</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
         <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="AA29" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.3</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE29" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AF29" t="n">
         <v>14</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
         <v>4</v>
       </c>
       <c r="AI29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK29" t="n">
         <v>23</v>
@@ -5683,49 +5750,49 @@
         <v>13</v>
       </c>
       <c r="AN29" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AO29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>6</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>5</v>
       </c>
       <c r="AR29" t="n">
         <v>7</v>
       </c>
       <c r="AS29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>14</v>
       </c>
       <c r="AU29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AV29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
         <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AY29" t="n">
         <v>17</v>
       </c>
       <c r="AZ29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA29" t="n">
         <v>4</v>
       </c>
       <c r="BB29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC29" t="n">
         <v>14</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5914,7 @@
         <v>29</v>
       </c>
       <c r="AH30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI30" t="n">
         <v>27</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>22</v>
@@ -5889,7 +5956,7 @@
         <v>25</v>
       </c>
       <c r="AV30" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>22</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6093,7 @@
         <v>12</v>
       </c>
       <c r="AG31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH31" t="n">
         <v>2</v>
@@ -6068,7 +6135,7 @@
         <v>17</v>
       </c>
       <c r="AU31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV31" t="n">
         <v>21</v>
@@ -6089,7 +6156,7 @@
         <v>21</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC31" t="n">
         <v>16</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-22-2013-14</t>
+          <t>2013-12-22</t>
         </is>
       </c>
     </row>
